--- a/study_case_model/scenario_variables/price_scenarios188.xlsx
+++ b/study_case_model/scenario_variables/price_scenarios188.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D321"/>
+  <dimension ref="A1:D385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.07314384442957</v>
+        <v>30.0853187380475</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28.5815362448472</v>
+        <v>23.12369601522129</v>
       </c>
     </row>
     <row r="4">
@@ -491,11 +491,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28.08520949642142</v>
+        <v>27.26532160975045</v>
       </c>
     </row>
     <row r="5">
@@ -507,11 +507,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.94588944009113</v>
+        <v>26.85861460724102</v>
       </c>
     </row>
     <row r="6">
@@ -523,11 +523,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.07017554808181</v>
+        <v>27.5733656442835</v>
       </c>
     </row>
     <row r="7">
@@ -535,15 +535,15 @@
         <v>3</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30.98529814591621</v>
+        <v>28.26613509053244</v>
       </c>
     </row>
     <row r="8">
@@ -555,11 +555,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>28.74053616513872</v>
+        <v>29.89369070365238</v>
       </c>
     </row>
     <row r="9">
@@ -571,11 +571,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>27.76717057398501</v>
+        <v>22.87845444676072</v>
       </c>
     </row>
     <row r="10">
@@ -587,11 +587,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>28.94254623475594</v>
+        <v>27.21995466117444</v>
       </c>
     </row>
     <row r="11">
@@ -603,11 +603,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20.3376175598914</v>
+        <v>27.03054725563269</v>
       </c>
     </row>
     <row r="12">
@@ -615,15 +615,15 @@
         <v>3</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31.17178453854761</v>
+        <v>28.49678574744939</v>
       </c>
     </row>
     <row r="13">
@@ -631,15 +631,15 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28.75569964544023</v>
+        <v>28.43509237705367</v>
       </c>
     </row>
     <row r="14">
@@ -651,11 +651,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>27.48188329759193</v>
+        <v>30.07374912477554</v>
       </c>
     </row>
     <row r="15">
@@ -667,11 +667,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>29.00135007775016</v>
+        <v>23.04631774045898</v>
       </c>
     </row>
     <row r="16">
@@ -683,11 +683,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>20.154425998306</v>
+        <v>26.74079508798118</v>
       </c>
     </row>
     <row r="17">
@@ -695,15 +695,15 @@
         <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>30.68579179755132</v>
+        <v>26.91463161036991</v>
       </c>
     </row>
     <row r="18">
@@ -711,15 +711,15 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>28.56416574235137</v>
+        <v>27.98607992743867</v>
       </c>
     </row>
     <row r="19">
@@ -727,15 +727,15 @@
         <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>27.74843494889589</v>
+        <v>29.08474204068694</v>
       </c>
     </row>
     <row r="20">
@@ -747,11 +747,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.09817675980411</v>
+        <v>29.93879149633678</v>
       </c>
     </row>
     <row r="21">
@@ -763,11 +763,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20.18629843006824</v>
+        <v>23.133034898786</v>
       </c>
     </row>
     <row r="22">
@@ -775,15 +775,15 @@
         <v>3</v>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>30.70078465104415</v>
+        <v>27.25446368892001</v>
       </c>
     </row>
     <row r="23">
@@ -791,15 +791,15 @@
         <v>3</v>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>28.36003210951093</v>
+        <v>26.60714080600722</v>
       </c>
     </row>
     <row r="24">
@@ -807,15 +807,15 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>27.58133450635064</v>
+        <v>28.28887278626872</v>
       </c>
     </row>
     <row r="25">
@@ -823,15 +823,15 @@
         <v>3</v>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.86325279198515</v>
+        <v>28.59897775964668</v>
       </c>
     </row>
     <row r="26">
@@ -843,11 +843,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>20.20113006691965</v>
+        <v>30.23377488268549</v>
       </c>
     </row>
     <row r="27">
@@ -855,15 +855,15 @@
         <v>3</v>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>31.26738079403982</v>
+        <v>22.85375110243023</v>
       </c>
     </row>
     <row r="28">
@@ -871,15 +871,15 @@
         <v>3</v>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>29.01701374787593</v>
+        <v>27.64638430427586</v>
       </c>
     </row>
     <row r="29">
@@ -887,7 +887,7 @@
         <v>3</v>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>27.72450128742832</v>
+        <v>26.54436650136627</v>
       </c>
     </row>
     <row r="30">
@@ -903,7 +903,7 @@
         <v>3</v>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>29.17162754921555</v>
+        <v>28.13337343288733</v>
       </c>
     </row>
     <row r="31">
@@ -919,7 +919,7 @@
         <v>3</v>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20.21870102648641</v>
+        <v>29.00731013014455</v>
       </c>
     </row>
     <row r="32">
@@ -935,7 +935,7 @@
         <v>3</v>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>30.54401792545246</v>
+        <v>29.69936687992453</v>
       </c>
     </row>
     <row r="33">
@@ -951,7 +951,7 @@
         <v>3</v>
       </c>
       <c r="B33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>28.47228008036276</v>
+        <v>22.93287955853662</v>
       </c>
     </row>
     <row r="34">
@@ -967,15 +967,15 @@
         <v>3</v>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>27.69285423352724</v>
+        <v>27.29109635655066</v>
       </c>
     </row>
     <row r="35">
@@ -983,15 +983,15 @@
         <v>3</v>
       </c>
       <c r="B35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>29.8134108078817</v>
+        <v>26.78622505916637</v>
       </c>
     </row>
     <row r="36">
@@ -999,15 +999,15 @@
         <v>3</v>
       </c>
       <c r="B36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>20.19484237346811</v>
+        <v>27.53552531550904</v>
       </c>
     </row>
     <row r="37">
@@ -1015,15 +1015,15 @@
         <v>3</v>
       </c>
       <c r="B37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>31.23545960766683</v>
+        <v>28.40499949542222</v>
       </c>
     </row>
     <row r="38">
@@ -1031,15 +1031,15 @@
         <v>3</v>
       </c>
       <c r="B38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>28.46994533391772</v>
+        <v>29.6778391801997</v>
       </c>
     </row>
     <row r="39">
@@ -1047,15 +1047,15 @@
         <v>3</v>
       </c>
       <c r="B39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>27.35273931579549</v>
+        <v>23.1727144963326</v>
       </c>
     </row>
     <row r="40">
@@ -1063,15 +1063,15 @@
         <v>3</v>
       </c>
       <c r="B40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>29.42921251240101</v>
+        <v>27.01325632417877</v>
       </c>
     </row>
     <row r="41">
@@ -1079,15 +1079,15 @@
         <v>3</v>
       </c>
       <c r="B41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>20.38590859462526</v>
+        <v>27.33903938453419</v>
       </c>
     </row>
     <row r="42">
@@ -1095,15 +1095,15 @@
         <v>3</v>
       </c>
       <c r="B42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>27.12533788709154</v>
+        <v>27.75016405294309</v>
       </c>
     </row>
     <row r="43">
@@ -1111,15 +1111,15 @@
         <v>3</v>
       </c>
       <c r="B43" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>26.46731212931615</v>
+        <v>28.29411863393847</v>
       </c>
     </row>
     <row r="44">
@@ -1127,15 +1127,15 @@
         <v>3</v>
       </c>
       <c r="B44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>31.39424654173239</v>
+        <v>30.24051967523399</v>
       </c>
     </row>
     <row r="45">
@@ -1143,15 +1143,15 @@
         <v>3</v>
       </c>
       <c r="B45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>30.59584849993491</v>
+        <v>22.77960732642177</v>
       </c>
     </row>
     <row r="46">
@@ -1159,15 +1159,15 @@
         <v>3</v>
       </c>
       <c r="B46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>19.23637478622206</v>
+        <v>27.32594199225768</v>
       </c>
     </row>
     <row r="47">
@@ -1175,15 +1175,15 @@
         <v>3</v>
       </c>
       <c r="B47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>27.50195711005667</v>
+        <v>27.27367557567923</v>
       </c>
     </row>
     <row r="48">
@@ -1191,15 +1191,15 @@
         <v>3</v>
       </c>
       <c r="B48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>26.44563709446718</v>
+        <v>27.51963325171168</v>
       </c>
     </row>
     <row r="49">
@@ -1207,15 +1207,15 @@
         <v>3</v>
       </c>
       <c r="B49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>30.78461678345882</v>
+        <v>28.43794683967966</v>
       </c>
     </row>
     <row r="50">
@@ -1223,15 +1223,15 @@
         <v>3</v>
       </c>
       <c r="B50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>31.06177753918042</v>
+        <v>32.07303485763677</v>
       </c>
     </row>
     <row r="51">
@@ -1239,15 +1239,15 @@
         <v>3</v>
       </c>
       <c r="B51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>19.02785798803784</v>
+        <v>30.84688142834338</v>
       </c>
     </row>
     <row r="52">
@@ -1255,15 +1255,15 @@
         <v>3</v>
       </c>
       <c r="B52" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>26.49513024725681</v>
+        <v>22.44592923236874</v>
       </c>
     </row>
     <row r="53">
@@ -1271,15 +1271,15 @@
         <v>3</v>
       </c>
       <c r="B53" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>26.72852475685374</v>
+        <v>26.77590993869613</v>
       </c>
     </row>
     <row r="54">
@@ -1287,15 +1287,15 @@
         <v>3</v>
       </c>
       <c r="B54" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>30.63105361729996</v>
+        <v>31.15555976851631</v>
       </c>
     </row>
     <row r="55">
@@ -1303,15 +1303,15 @@
         <v>3</v>
       </c>
       <c r="B55" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>31.17781464852496</v>
+        <v>29.89314116689913</v>
       </c>
     </row>
     <row r="56">
@@ -1319,15 +1319,15 @@
         <v>3</v>
       </c>
       <c r="B56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>18.94831138513049</v>
+        <v>32.07003102410232</v>
       </c>
     </row>
     <row r="57">
@@ -1335,15 +1335,15 @@
         <v>3</v>
       </c>
       <c r="B57" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>27.32957714526997</v>
+        <v>30.71362376141913</v>
       </c>
     </row>
     <row r="58">
@@ -1351,15 +1351,15 @@
         <v>3</v>
       </c>
       <c r="B58" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>26.50100283080854</v>
+        <v>22.57250208966166</v>
       </c>
     </row>
     <row r="59">
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="B59" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>30.86023217403964</v>
+        <v>27.1972255427317</v>
       </c>
     </row>
     <row r="60">
@@ -1383,7 +1383,7 @@
         <v>3</v>
       </c>
       <c r="B60" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>31.28329621575929</v>
+        <v>31.08462456199494</v>
       </c>
     </row>
     <row r="61">
@@ -1399,7 +1399,7 @@
         <v>3</v>
       </c>
       <c r="B61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>18.88875113722388</v>
+        <v>29.59171622733891</v>
       </c>
     </row>
     <row r="62">
@@ -1415,7 +1415,7 @@
         <v>3</v>
       </c>
       <c r="B62" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>26.97366684091011</v>
+        <v>32.58675798974242</v>
       </c>
     </row>
     <row r="63">
@@ -1431,7 +1431,7 @@
         <v>3</v>
       </c>
       <c r="B63" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>27.05935203482123</v>
+        <v>30.75261314439343</v>
       </c>
     </row>
     <row r="64">
@@ -1447,15 +1447,15 @@
         <v>3</v>
       </c>
       <c r="B64" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>30.46226635258101</v>
+        <v>22.45630349820185</v>
       </c>
     </row>
     <row r="65">
@@ -1463,15 +1463,15 @@
         <v>3</v>
       </c>
       <c r="B65" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>31.08814833338504</v>
+        <v>27.31235595200049</v>
       </c>
     </row>
     <row r="66">
@@ -1479,15 +1479,15 @@
         <v>3</v>
       </c>
       <c r="B66" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>19.17384375231396</v>
+        <v>30.69169950130432</v>
       </c>
     </row>
     <row r="67">
@@ -1495,15 +1495,15 @@
         <v>3</v>
       </c>
       <c r="B67" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>27.12285949914982</v>
+        <v>30.03921361819298</v>
       </c>
     </row>
     <row r="68">
@@ -1511,15 +1511,15 @@
         <v>3</v>
       </c>
       <c r="B68" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>26.37981929101224</v>
+        <v>32.36053216632335</v>
       </c>
     </row>
     <row r="69">
@@ -1527,15 +1527,15 @@
         <v>3</v>
       </c>
       <c r="B69" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>30.55112962878479</v>
+        <v>30.35639330082552</v>
       </c>
     </row>
     <row r="70">
@@ -1543,15 +1543,15 @@
         <v>3</v>
       </c>
       <c r="B70" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>31.19281779843141</v>
+        <v>22.9459986499997</v>
       </c>
     </row>
     <row r="71">
@@ -1559,15 +1559,15 @@
         <v>3</v>
       </c>
       <c r="B71" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>19.18093916885291</v>
+        <v>27.24621017196735</v>
       </c>
     </row>
     <row r="72">
@@ -1575,15 +1575,15 @@
         <v>3</v>
       </c>
       <c r="B72" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>26.97986556325624</v>
+        <v>31.24857789629164</v>
       </c>
     </row>
     <row r="73">
@@ -1591,15 +1591,15 @@
         <v>3</v>
       </c>
       <c r="B73" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>26.80274849060388</v>
+        <v>30.36995805017136</v>
       </c>
     </row>
     <row r="74">
@@ -1607,15 +1607,15 @@
         <v>3</v>
       </c>
       <c r="B74" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>30.74940697243934</v>
+        <v>31.91139920571509</v>
       </c>
     </row>
     <row r="75">
@@ -1623,15 +1623,15 @@
         <v>3</v>
       </c>
       <c r="B75" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>31.10292517639861</v>
+        <v>30.37688390136735</v>
       </c>
     </row>
     <row r="76">
@@ -1639,15 +1639,15 @@
         <v>3</v>
       </c>
       <c r="B76" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>19.18019099412757</v>
+        <v>22.52489125549262</v>
       </c>
     </row>
     <row r="77">
@@ -1655,15 +1655,15 @@
         <v>3</v>
       </c>
       <c r="B77" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>26.72020231462741</v>
+        <v>26.9128417096471</v>
       </c>
     </row>
     <row r="78">
@@ -1671,15 +1671,15 @@
         <v>3</v>
       </c>
       <c r="B78" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>27.20856375825748</v>
+        <v>30.96989355208163</v>
       </c>
     </row>
     <row r="79">
@@ -1687,15 +1687,15 @@
         <v>3</v>
       </c>
       <c r="B79" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>31.10664063201015</v>
+        <v>29.90630506594851</v>
       </c>
     </row>
     <row r="80">
@@ -1703,15 +1703,15 @@
         <v>3</v>
       </c>
       <c r="B80" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>30.66118320944262</v>
+        <v>32.07841172142162</v>
       </c>
     </row>
     <row r="81">
@@ -1719,15 +1719,15 @@
         <v>3</v>
       </c>
       <c r="B81" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>19.24970364765951</v>
+        <v>30.86076514406685</v>
       </c>
     </row>
     <row r="82">
@@ -1735,15 +1735,15 @@
         <v>3</v>
       </c>
       <c r="B82" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>29.64802534444606</v>
+        <v>22.73000660611551</v>
       </c>
     </row>
     <row r="83">
@@ -1751,15 +1751,15 @@
         <v>3</v>
       </c>
       <c r="B83" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>27.13366671852769</v>
+        <v>27.52861026891005</v>
       </c>
     </row>
     <row r="84">
@@ -1767,15 +1767,15 @@
         <v>3</v>
       </c>
       <c r="B84" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>26.40706535383254</v>
+        <v>30.91176311031762</v>
       </c>
     </row>
     <row r="85">
@@ -1783,15 +1783,15 @@
         <v>3</v>
       </c>
       <c r="B85" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>31.57376441357289</v>
+        <v>30.61536224233168</v>
       </c>
     </row>
     <row r="86">
@@ -1799,15 +1799,15 @@
         <v>3</v>
       </c>
       <c r="B86" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>30.3101123041779</v>
+        <v>32.19004896545693</v>
       </c>
     </row>
     <row r="87">
@@ -1815,15 +1815,15 @@
         <v>3</v>
       </c>
       <c r="B87" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>30.06342947481396</v>
+        <v>30.34522911157405</v>
       </c>
     </row>
     <row r="88">
@@ -1831,15 +1831,15 @@
         <v>3</v>
       </c>
       <c r="B88" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>27.14308275720337</v>
+        <v>22.48366936818038</v>
       </c>
     </row>
     <row r="89">
@@ -1847,7 +1847,7 @@
         <v>3</v>
       </c>
       <c r="B89" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>26.59976896908686</v>
+        <v>27.2651204035143</v>
       </c>
     </row>
     <row r="90">
@@ -1863,7 +1863,7 @@
         <v>3</v>
       </c>
       <c r="B90" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>31.75690948895807</v>
+        <v>30.92453070714119</v>
       </c>
     </row>
     <row r="91">
@@ -1879,7 +1879,7 @@
         <v>3</v>
       </c>
       <c r="B91" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>29.79461977160518</v>
+        <v>30.01743117264935</v>
       </c>
     </row>
     <row r="92">
@@ -1895,7 +1895,7 @@
         <v>3</v>
       </c>
       <c r="B92" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>29.67352428300508</v>
+        <v>32.14128685154849</v>
       </c>
     </row>
     <row r="93">
@@ -1911,7 +1911,7 @@
         <v>3</v>
       </c>
       <c r="B93" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>26.7021390494218</v>
+        <v>30.58529316266471</v>
       </c>
     </row>
     <row r="94">
@@ -1927,15 +1927,15 @@
         <v>3</v>
       </c>
       <c r="B94" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>26.08449129212155</v>
+        <v>22.53460041367748</v>
       </c>
     </row>
     <row r="95">
@@ -1943,15 +1943,15 @@
         <v>3</v>
       </c>
       <c r="B95" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>31.94363469618419</v>
+        <v>26.72316359096767</v>
       </c>
     </row>
     <row r="96">
@@ -1959,15 +1959,15 @@
         <v>3</v>
       </c>
       <c r="B96" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>30.10396320075756</v>
+        <v>30.85539838633474</v>
       </c>
     </row>
     <row r="97">
@@ -1975,15 +1975,15 @@
         <v>3</v>
       </c>
       <c r="B97" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>30.18750088155753</v>
+        <v>30.05987245345765</v>
       </c>
     </row>
     <row r="98">
@@ -1991,15 +1991,15 @@
         <v>3</v>
       </c>
       <c r="B98" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>26.92526995421126</v>
+        <v>27.66950683805296</v>
       </c>
     </row>
     <row r="99">
@@ -2007,15 +2007,15 @@
         <v>3</v>
       </c>
       <c r="B99" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>26.48405792328674</v>
+        <v>27.13782391973364</v>
       </c>
     </row>
     <row r="100">
@@ -2023,15 +2023,15 @@
         <v>3</v>
       </c>
       <c r="B100" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>31.75077528726408</v>
+        <v>21.7228483936089</v>
       </c>
     </row>
     <row r="101">
@@ -2039,15 +2039,15 @@
         <v>3</v>
       </c>
       <c r="B101" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>30.83751735241013</v>
+        <v>24.74560458124206</v>
       </c>
     </row>
     <row r="102">
@@ -2055,15 +2055,15 @@
         <v>3</v>
       </c>
       <c r="B102" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>30.12716733606671</v>
+        <v>32.1508755266154</v>
       </c>
     </row>
     <row r="103">
@@ -2071,15 +2071,15 @@
         <v>3</v>
       </c>
       <c r="B103" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>26.69100763225978</v>
+        <v>31.33743567651315</v>
       </c>
     </row>
     <row r="104">
@@ -2087,15 +2087,15 @@
         <v>3</v>
       </c>
       <c r="B104" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>25.82506599905941</v>
+        <v>27.62646636716737</v>
       </c>
     </row>
     <row r="105">
@@ -2103,15 +2103,15 @@
         <v>3</v>
       </c>
       <c r="B105" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>31.98862409918828</v>
+        <v>27.1660648574326</v>
       </c>
     </row>
     <row r="106">
@@ -2119,15 +2119,15 @@
         <v>3</v>
       </c>
       <c r="B106" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>29.95381260257579</v>
+        <v>21.76288084093663</v>
       </c>
     </row>
     <row r="107">
@@ -2135,15 +2135,15 @@
         <v>3</v>
       </c>
       <c r="B107" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>30.15361414184559</v>
+        <v>24.78885832333376</v>
       </c>
     </row>
     <row r="108">
@@ -2151,15 +2151,15 @@
         <v>3</v>
       </c>
       <c r="B108" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>27.04917355785272</v>
+        <v>32.78889305319687</v>
       </c>
     </row>
     <row r="109">
@@ -2167,15 +2167,15 @@
         <v>3</v>
       </c>
       <c r="B109" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>26.08560668940999</v>
+        <v>31.61906377743652</v>
       </c>
     </row>
     <row r="110">
@@ -2183,15 +2183,15 @@
         <v>3</v>
       </c>
       <c r="B110" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>31.56545184193563</v>
+        <v>27.23001475995352</v>
       </c>
     </row>
     <row r="111">
@@ -2199,15 +2199,15 @@
         <v>3</v>
       </c>
       <c r="B111" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>29.56612739546897</v>
+        <v>27.22243909200669</v>
       </c>
     </row>
     <row r="112">
@@ -2215,15 +2215,15 @@
         <v>3</v>
       </c>
       <c r="B112" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>29.80615763334173</v>
+        <v>21.79698051122132</v>
       </c>
     </row>
     <row r="113">
@@ -2231,15 +2231,15 @@
         <v>3</v>
       </c>
       <c r="B113" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>27.1523273252263</v>
+        <v>24.77727288241</v>
       </c>
     </row>
     <row r="114">
@@ -2247,15 +2247,15 @@
         <v>3</v>
       </c>
       <c r="B114" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>26.16050675406494</v>
+        <v>32.60464645942106</v>
       </c>
     </row>
     <row r="115">
@@ -2263,15 +2263,15 @@
         <v>3</v>
       </c>
       <c r="B115" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>31.43844756671817</v>
+        <v>32.49483021700793</v>
       </c>
     </row>
     <row r="116">
@@ -2279,15 +2279,15 @@
         <v>3</v>
       </c>
       <c r="B116" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>30.07288860707798</v>
+        <v>27.7680198336144</v>
       </c>
     </row>
     <row r="117">
@@ -2295,15 +2295,15 @@
         <v>3</v>
       </c>
       <c r="B117" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>30.05520693175735</v>
+        <v>27.79221006186055</v>
       </c>
     </row>
     <row r="118">
@@ -2311,15 +2311,15 @@
         <v>3</v>
       </c>
       <c r="B118" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>26.68381955213667</v>
+        <v>21.8921716847523</v>
       </c>
     </row>
     <row r="119">
@@ -2327,7 +2327,7 @@
         <v>3</v>
       </c>
       <c r="B119" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>26.14474775143408</v>
+        <v>24.8111934441087</v>
       </c>
     </row>
     <row r="120">
@@ -2343,7 +2343,7 @@
         <v>3</v>
       </c>
       <c r="B120" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>31.85355962884272</v>
+        <v>32.33531176172219</v>
       </c>
     </row>
     <row r="121">
@@ -2359,7 +2359,7 @@
         <v>3</v>
       </c>
       <c r="B121" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>29.67776818887792</v>
+        <v>31.52681254180862</v>
       </c>
     </row>
     <row r="122">
@@ -2375,7 +2375,7 @@
         <v>3</v>
       </c>
       <c r="B122" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>31.81413348734931</v>
+        <v>27.39701461809451</v>
       </c>
     </row>
     <row r="123">
@@ -2391,7 +2391,7 @@
         <v>3</v>
       </c>
       <c r="B123" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>25.79403323672387</v>
+        <v>27.41507674545921</v>
       </c>
     </row>
     <row r="124">
@@ -2407,15 +2407,15 @@
         <v>3</v>
       </c>
       <c r="B124" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>27.42808269595969</v>
+        <v>21.58004109099569</v>
       </c>
     </row>
     <row r="125">
@@ -2423,15 +2423,15 @@
         <v>3</v>
       </c>
       <c r="B125" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>31.32040349233448</v>
+        <v>24.67080393674179</v>
       </c>
     </row>
     <row r="126">
@@ -2439,15 +2439,15 @@
         <v>3</v>
       </c>
       <c r="B126" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>29.3940167931992</v>
+        <v>33.1883966328481</v>
       </c>
     </row>
     <row r="127">
@@ -2455,15 +2455,15 @@
         <v>3</v>
       </c>
       <c r="B127" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>31.40341512723</v>
+        <v>30.70508122922451</v>
       </c>
     </row>
     <row r="128">
@@ -2471,15 +2471,15 @@
         <v>3</v>
       </c>
       <c r="B128" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>25.7822984643981</v>
+        <v>27.79987385755037</v>
       </c>
     </row>
     <row r="129">
@@ -2487,15 +2487,15 @@
         <v>3</v>
       </c>
       <c r="B129" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>27.27361708258432</v>
+        <v>27.03697804640046</v>
       </c>
     </row>
     <row r="130">
@@ -2503,15 +2503,15 @@
         <v>3</v>
       </c>
       <c r="B130" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>31.15342309401957</v>
+        <v>21.5829537906816</v>
       </c>
     </row>
     <row r="131">
@@ -2519,15 +2519,15 @@
         <v>3</v>
       </c>
       <c r="B131" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>30.95291820718838</v>
+        <v>24.91905454203809</v>
       </c>
     </row>
     <row r="132">
@@ -2535,15 +2535,15 @@
         <v>3</v>
       </c>
       <c r="B132" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>31.88168870403921</v>
+        <v>32.45842834817261</v>
       </c>
     </row>
     <row r="133">
@@ -2551,15 +2551,15 @@
         <v>3</v>
       </c>
       <c r="B133" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>25.94146568987493</v>
+        <v>30.95211692543657</v>
       </c>
     </row>
     <row r="134">
@@ -2567,15 +2567,15 @@
         <v>3</v>
       </c>
       <c r="B134" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>27.39306614514273</v>
+        <v>27.41289653274493</v>
       </c>
     </row>
     <row r="135">
@@ -2583,15 +2583,15 @@
         <v>3</v>
       </c>
       <c r="B135" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>31.19568113263524</v>
+        <v>27.66690937920993</v>
       </c>
     </row>
     <row r="136">
@@ -2599,15 +2599,15 @@
         <v>3</v>
       </c>
       <c r="B136" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>29.71066117653243</v>
+        <v>21.52691145292214</v>
       </c>
     </row>
     <row r="137">
@@ -2615,15 +2615,15 @@
         <v>3</v>
       </c>
       <c r="B137" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>31.94131099481595</v>
+        <v>24.70397984009355</v>
       </c>
     </row>
     <row r="138">
@@ -2631,15 +2631,15 @@
         <v>3</v>
       </c>
       <c r="B138" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>25.45195979185408</v>
+        <v>32.45235986805462</v>
       </c>
     </row>
     <row r="139">
@@ -2647,15 +2647,15 @@
         <v>3</v>
       </c>
       <c r="B139" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>27.0699465005624</v>
+        <v>31.0854546885606</v>
       </c>
     </row>
     <row r="140">
@@ -2663,15 +2663,15 @@
         <v>3</v>
       </c>
       <c r="B140" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>30.843357734032</v>
+        <v>28.20234613567843</v>
       </c>
     </row>
     <row r="141">
@@ -2679,15 +2679,15 @@
         <v>3</v>
       </c>
       <c r="B141" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>29.82902827680855</v>
+        <v>27.65435679439516</v>
       </c>
     </row>
     <row r="142">
@@ -2695,15 +2695,15 @@
         <v>3</v>
       </c>
       <c r="B142" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>32.43447559943716</v>
+        <v>21.24613548561328</v>
       </c>
     </row>
     <row r="143">
@@ -2711,15 +2711,15 @@
         <v>3</v>
       </c>
       <c r="B143" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>25.17123384781447</v>
+        <v>24.69658359988992</v>
       </c>
     </row>
     <row r="144">
@@ -2727,15 +2727,15 @@
         <v>3</v>
       </c>
       <c r="B144" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>27.32041659689177</v>
+        <v>32.22290997000602</v>
       </c>
     </row>
     <row r="145">
@@ -2743,15 +2743,15 @@
         <v>3</v>
       </c>
       <c r="B145" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>30.49394851905272</v>
+        <v>31.55605684267644</v>
       </c>
     </row>
     <row r="146">
@@ -2759,15 +2759,15 @@
         <v>3</v>
       </c>
       <c r="B146" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>29.66396846822377</v>
+        <v>28.5629946491987</v>
       </c>
     </row>
     <row r="147">
@@ -2775,15 +2775,15 @@
         <v>3</v>
       </c>
       <c r="B147" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>32.04591744176552</v>
+        <v>30.77454194026616</v>
       </c>
     </row>
     <row r="148">
@@ -2791,15 +2791,15 @@
         <v>3</v>
       </c>
       <c r="B148" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>25.66667888260764</v>
+        <v>27.54879943231923</v>
       </c>
     </row>
     <row r="149">
@@ -2807,7 +2807,7 @@
         <v>3</v>
       </c>
       <c r="B149" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>26.84176786645005</v>
+        <v>26.42043769967777</v>
       </c>
     </row>
     <row r="150">
@@ -2823,7 +2823,7 @@
         <v>3</v>
       </c>
       <c r="B150" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>30.77209056259594</v>
+        <v>30.71108443900398</v>
       </c>
     </row>
     <row r="151">
@@ -2839,7 +2839,7 @@
         <v>3</v>
       </c>
       <c r="B151" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>30.0071775631229</v>
+        <v>31.89130775774083</v>
       </c>
     </row>
     <row r="152">
@@ -2855,7 +2855,7 @@
         <v>3</v>
       </c>
       <c r="B152" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>31.46918092044926</v>
+        <v>28.65442833239878</v>
       </c>
     </row>
     <row r="153">
@@ -2871,7 +2871,7 @@
         <v>3</v>
       </c>
       <c r="B153" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>25.70571297649955</v>
+        <v>30.60860208239184</v>
       </c>
     </row>
     <row r="154">
@@ -2887,15 +2887,15 @@
         <v>3</v>
       </c>
       <c r="B154" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>27.14657090423679</v>
+        <v>27.89429822245935</v>
       </c>
     </row>
     <row r="155">
@@ -2903,15 +2903,15 @@
         <v>3</v>
       </c>
       <c r="B155" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>30.79183464891739</v>
+        <v>26.29974423851887</v>
       </c>
     </row>
     <row r="156">
@@ -2919,15 +2919,15 @@
         <v>3</v>
       </c>
       <c r="B156" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>30.44362051315919</v>
+        <v>30.69225129262015</v>
       </c>
     </row>
     <row r="157">
@@ -2935,15 +2935,15 @@
         <v>3</v>
       </c>
       <c r="B157" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>31.90166919120501</v>
+        <v>32.2920432197155</v>
       </c>
     </row>
     <row r="158">
@@ -2951,15 +2951,15 @@
         <v>3</v>
       </c>
       <c r="B158" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>25.13073799479341</v>
+        <v>29.40216425950368</v>
       </c>
     </row>
     <row r="159">
@@ -2967,15 +2967,15 @@
         <v>3</v>
       </c>
       <c r="B159" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>27.18479824426563</v>
+        <v>31.12799354698901</v>
       </c>
     </row>
     <row r="160">
@@ -2983,15 +2983,15 @@
         <v>3</v>
       </c>
       <c r="B160" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>30.7886775851249</v>
+        <v>26.99391540885022</v>
       </c>
     </row>
     <row r="161">
@@ -2999,15 +2999,15 @@
         <v>3</v>
       </c>
       <c r="B161" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>30.05869056307655</v>
+        <v>26.06682603775835</v>
       </c>
     </row>
     <row r="162">
@@ -3015,15 +3015,15 @@
         <v>3</v>
       </c>
       <c r="B162" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>27.39157660620682</v>
+        <v>31.4779958449378</v>
       </c>
     </row>
     <row r="163">
@@ -3031,15 +3031,15 @@
         <v>3</v>
       </c>
       <c r="B163" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>27.44862511353923</v>
+        <v>31.77190010906777</v>
       </c>
     </row>
     <row r="164">
@@ -3047,15 +3047,15 @@
         <v>3</v>
       </c>
       <c r="B164" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>25.02801532842905</v>
+        <v>28.918951456341</v>
       </c>
     </row>
     <row r="165">
@@ -3063,15 +3063,15 @@
         <v>3</v>
       </c>
       <c r="B165" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>26.64003802306607</v>
+        <v>31.04855603023831</v>
       </c>
     </row>
     <row r="166">
@@ -3079,15 +3079,15 @@
         <v>3</v>
       </c>
       <c r="B166" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>28.81873804031774</v>
+        <v>27.15630532847723</v>
       </c>
     </row>
     <row r="167">
@@ -3095,15 +3095,15 @@
         <v>3</v>
       </c>
       <c r="B167" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>27.51803759872232</v>
+        <v>26.17807281493502</v>
       </c>
     </row>
     <row r="168">
@@ -3111,15 +3111,15 @@
         <v>3</v>
       </c>
       <c r="B168" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>27.34963915830861</v>
+        <v>30.07666522131515</v>
       </c>
     </row>
     <row r="169">
@@ -3127,15 +3127,15 @@
         <v>3</v>
       </c>
       <c r="B169" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>24.73956831508951</v>
+        <v>31.67055554209665</v>
       </c>
     </row>
     <row r="170">
@@ -3143,15 +3143,15 @@
         <v>3</v>
       </c>
       <c r="B170" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>26.87766095814025</v>
+        <v>28.7184533199484</v>
       </c>
     </row>
     <row r="171">
@@ -3159,15 +3159,15 @@
         <v>3</v>
       </c>
       <c r="B171" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>29.28697921799959</v>
+        <v>30.42545146191644</v>
       </c>
     </row>
     <row r="172">
@@ -3175,15 +3175,15 @@
         <v>3</v>
       </c>
       <c r="B172" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>27.26225967361856</v>
+        <v>27.85783064738067</v>
       </c>
     </row>
     <row r="173">
@@ -3191,15 +3191,15 @@
         <v>3</v>
       </c>
       <c r="B173" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>27.732384749842</v>
+        <v>25.81905825001109</v>
       </c>
     </row>
     <row r="174">
@@ -3207,15 +3207,15 @@
         <v>3</v>
       </c>
       <c r="B174" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>25.43072697055701</v>
+        <v>30.94740256620453</v>
       </c>
     </row>
     <row r="175">
@@ -3223,15 +3223,15 @@
         <v>3</v>
       </c>
       <c r="B175" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>26.6840684524092</v>
+        <v>32.04017742706655</v>
       </c>
     </row>
     <row r="176">
@@ -3239,15 +3239,15 @@
         <v>3</v>
       </c>
       <c r="B176" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>28.72566795027612</v>
+        <v>29.2061300995677</v>
       </c>
     </row>
     <row r="177">
@@ -3255,15 +3255,15 @@
         <v>3</v>
       </c>
       <c r="B177" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>27.47669577140877</v>
+        <v>30.36750453441212</v>
       </c>
     </row>
     <row r="178">
@@ -3271,15 +3271,15 @@
         <v>3</v>
       </c>
       <c r="B178" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>27.82830401114407</v>
+        <v>27.72920810796261</v>
       </c>
     </row>
     <row r="179">
@@ -3287,7 +3287,7 @@
         <v>3</v>
       </c>
       <c r="B179" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>24.72603636784567</v>
+        <v>26.19634510079635</v>
       </c>
     </row>
     <row r="180">
@@ -3303,7 +3303,7 @@
         <v>3</v>
       </c>
       <c r="B180" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>26.52859896400653</v>
+        <v>30.77909283381314</v>
       </c>
     </row>
     <row r="181">
@@ -3319,7 +3319,7 @@
         <v>3</v>
       </c>
       <c r="B181" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>29.39480255791037</v>
+        <v>32.14620806212114</v>
       </c>
     </row>
     <row r="182">
@@ -3335,7 +3335,7 @@
         <v>3</v>
       </c>
       <c r="B182" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>27.35446554835638</v>
+        <v>28.84848226405982</v>
       </c>
     </row>
     <row r="183">
@@ -3351,7 +3351,7 @@
         <v>3</v>
       </c>
       <c r="B183" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>27.46379720531138</v>
+        <v>30.62496594179443</v>
       </c>
     </row>
     <row r="184">
@@ -3367,15 +3367,15 @@
         <v>3</v>
       </c>
       <c r="B184" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>24.09511318527959</v>
+        <v>27.42951351477685</v>
       </c>
     </row>
     <row r="185">
@@ -3383,15 +3383,15 @@
         <v>3</v>
       </c>
       <c r="B185" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>26.14082521382341</v>
+        <v>26.09273693554986</v>
       </c>
     </row>
     <row r="186">
@@ -3399,15 +3399,15 @@
         <v>3</v>
       </c>
       <c r="B186" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>29.09517948032322</v>
+        <v>31.1194727601923</v>
       </c>
     </row>
     <row r="187">
@@ -3415,15 +3415,15 @@
         <v>3</v>
       </c>
       <c r="B187" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>27.26587684858006</v>
+        <v>32.21021345097125</v>
       </c>
     </row>
     <row r="188">
@@ -3431,15 +3431,15 @@
         <v>3</v>
       </c>
       <c r="B188" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>27.92874401970106</v>
+        <v>29.24780345545017</v>
       </c>
     </row>
     <row r="189">
@@ -3447,15 +3447,15 @@
         <v>3</v>
       </c>
       <c r="B189" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>24.54612451883205</v>
+        <v>30.42852249433754</v>
       </c>
     </row>
     <row r="190">
@@ -3463,15 +3463,15 @@
         <v>3</v>
       </c>
       <c r="B190" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>26.2951583056452</v>
+        <v>27.99505306182169</v>
       </c>
     </row>
     <row r="191">
@@ -3479,15 +3479,15 @@
         <v>3</v>
       </c>
       <c r="B191" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>29.20698623113986</v>
+        <v>25.68234135450083</v>
       </c>
     </row>
     <row r="192">
@@ -3495,15 +3495,15 @@
         <v>3</v>
       </c>
       <c r="B192" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>28.0083359542132</v>
+        <v>31.03700565402474</v>
       </c>
     </row>
     <row r="193">
@@ -3511,15 +3511,15 @@
         <v>3</v>
       </c>
       <c r="B193" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>27.08557772254438</v>
+        <v>32.18659436457719</v>
       </c>
     </row>
     <row r="194">
@@ -3527,15 +3527,15 @@
         <v>3</v>
       </c>
       <c r="B194" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>25.19191615868036</v>
+        <v>28.97730019028065</v>
       </c>
     </row>
     <row r="195">
@@ -3543,15 +3543,15 @@
         <v>3</v>
       </c>
       <c r="B195" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>26.41408282040258</v>
+        <v>32.17936589084081</v>
       </c>
     </row>
     <row r="196">
@@ -3559,15 +3559,15 @@
         <v>3</v>
       </c>
       <c r="B196" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>28.88255591423359</v>
+        <v>15.7501461715677</v>
       </c>
     </row>
     <row r="197">
@@ -3575,15 +3575,15 @@
         <v>3</v>
       </c>
       <c r="B197" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>27.73798330346252</v>
+        <v>30.1519411868662</v>
       </c>
     </row>
     <row r="198">
@@ -3591,15 +3591,15 @@
         <v>3</v>
       </c>
       <c r="B198" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>27.53485677795938</v>
+        <v>30.0827927034048</v>
       </c>
     </row>
     <row r="199">
@@ -3607,15 +3607,15 @@
         <v>3</v>
       </c>
       <c r="B199" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>24.75279449302796</v>
+        <v>25.04486042480135</v>
       </c>
     </row>
     <row r="200">
@@ -3623,15 +3623,15 @@
         <v>3</v>
       </c>
       <c r="B200" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>26.4298158217618</v>
+        <v>28.99926805443888</v>
       </c>
     </row>
     <row r="201">
@@ -3639,15 +3639,15 @@
         <v>3</v>
       </c>
       <c r="B201" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>29.05645915951369</v>
+        <v>32.15663116474247</v>
       </c>
     </row>
     <row r="202">
@@ -3655,15 +3655,15 @@
         <v>3</v>
       </c>
       <c r="B202" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>32.97048085923768</v>
+        <v>15.92497788925971</v>
       </c>
     </row>
     <row r="203">
@@ -3671,15 +3671,15 @@
         <v>3</v>
       </c>
       <c r="B203" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>27.98243320535048</v>
+        <v>30.39444284497853</v>
       </c>
     </row>
     <row r="204">
@@ -3687,15 +3687,15 @@
         <v>3</v>
       </c>
       <c r="B204" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>31.29854218406349</v>
+        <v>30.507122558296</v>
       </c>
     </row>
     <row r="205">
@@ -3703,15 +3703,15 @@
         <v>3</v>
       </c>
       <c r="B205" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>30.70013426519271</v>
+        <v>24.99023254966304</v>
       </c>
     </row>
     <row r="206">
@@ -3719,15 +3719,15 @@
         <v>3</v>
       </c>
       <c r="B206" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>23.98495521772896</v>
+        <v>28.65655722203655</v>
       </c>
     </row>
     <row r="207">
@@ -3735,15 +3735,15 @@
         <v>3</v>
       </c>
       <c r="B207" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>32.29021313221694</v>
+        <v>32.19961000112582</v>
       </c>
     </row>
     <row r="208">
@@ -3751,15 +3751,15 @@
         <v>3</v>
       </c>
       <c r="B208" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>27.75617787473323</v>
+        <v>15.90093939961181</v>
       </c>
     </row>
     <row r="209">
@@ -3767,7 +3767,7 @@
         <v>3</v>
       </c>
       <c r="B209" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>30.99115201070424</v>
+        <v>30.48627730236517</v>
       </c>
     </row>
     <row r="210">
@@ -3783,7 +3783,7 @@
         <v>3</v>
       </c>
       <c r="B210" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>31.17225413892696</v>
+        <v>30.25481614385098</v>
       </c>
     </row>
     <row r="211">
@@ -3799,7 +3799,7 @@
         <v>3</v>
       </c>
       <c r="B211" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>23.33779799658202</v>
+        <v>24.86300826459261</v>
       </c>
     </row>
     <row r="212">
@@ -3815,7 +3815,7 @@
         <v>3</v>
       </c>
       <c r="B212" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>32.86455498217542</v>
+        <v>29.26529986985653</v>
       </c>
     </row>
     <row r="213">
@@ -3831,7 +3831,7 @@
         <v>3</v>
       </c>
       <c r="B213" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>27.66132542747342</v>
+        <v>32.1894454916311</v>
       </c>
     </row>
     <row r="214">
@@ -3847,15 +3847,15 @@
         <v>3</v>
       </c>
       <c r="B214" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>30.62830946832464</v>
+        <v>15.86934244140877</v>
       </c>
     </row>
     <row r="215">
@@ -3863,15 +3863,15 @@
         <v>3</v>
       </c>
       <c r="B215" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>31.34900610600637</v>
+        <v>30.24005995544189</v>
       </c>
     </row>
     <row r="216">
@@ -3879,15 +3879,15 @@
         <v>3</v>
       </c>
       <c r="B216" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>23.56787459142578</v>
+        <v>30.1952683884298</v>
       </c>
     </row>
     <row r="217">
@@ -3895,15 +3895,15 @@
         <v>3</v>
       </c>
       <c r="B217" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>32.70489950008087</v>
+        <v>25.10674016284441</v>
       </c>
     </row>
     <row r="218">
@@ -3911,15 +3911,15 @@
         <v>3</v>
       </c>
       <c r="B218" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>28.04844577639707</v>
+        <v>29.13461765723405</v>
       </c>
     </row>
     <row r="219">
@@ -3927,15 +3927,15 @@
         <v>3</v>
       </c>
       <c r="B219" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>30.90457076494689</v>
+        <v>32.64442480970493</v>
       </c>
     </row>
     <row r="220">
@@ -3943,15 +3943,15 @@
         <v>3</v>
       </c>
       <c r="B220" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>31.33758551756165</v>
+        <v>15.98903773708224</v>
       </c>
     </row>
     <row r="221">
@@ -3959,15 +3959,15 @@
         <v>3</v>
       </c>
       <c r="B221" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>23.63189520178438</v>
+        <v>30.30769145498891</v>
       </c>
     </row>
     <row r="222">
@@ -3975,15 +3975,15 @@
         <v>3</v>
       </c>
       <c r="B222" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>32.66008235938634</v>
+        <v>30.46750795630783</v>
       </c>
     </row>
     <row r="223">
@@ -3991,15 +3991,15 @@
         <v>3</v>
       </c>
       <c r="B223" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>27.64265045205464</v>
+        <v>24.75682008606106</v>
       </c>
     </row>
     <row r="224">
@@ -4007,15 +4007,15 @@
         <v>3</v>
       </c>
       <c r="B224" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>31.04013246761169</v>
+        <v>28.98977593450654</v>
       </c>
     </row>
     <row r="225">
@@ -4023,15 +4023,15 @@
         <v>3</v>
       </c>
       <c r="B225" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>31.2746411110709</v>
+        <v>32.33886061093406</v>
       </c>
     </row>
     <row r="226">
@@ -4039,15 +4039,15 @@
         <v>3</v>
       </c>
       <c r="B226" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>23.47912441982493</v>
+        <v>15.79830296147626</v>
       </c>
     </row>
     <row r="227">
@@ -4055,15 +4055,15 @@
         <v>3</v>
       </c>
       <c r="B227" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>32.97173562273197</v>
+        <v>30.48166748876465</v>
       </c>
     </row>
     <row r="228">
@@ -4071,15 +4071,15 @@
         <v>3</v>
       </c>
       <c r="B228" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>28.15354169587025</v>
+        <v>30.01353828839505</v>
       </c>
     </row>
     <row r="229">
@@ -4087,15 +4087,15 @@
         <v>3</v>
       </c>
       <c r="B229" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>30.62762960741948</v>
+        <v>25.35349209701874</v>
       </c>
     </row>
     <row r="230">
@@ -4103,15 +4103,15 @@
         <v>3</v>
       </c>
       <c r="B230" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>31.25497279316113</v>
+        <v>28.60540465286982</v>
       </c>
     </row>
     <row r="231">
@@ -4119,15 +4119,15 @@
         <v>3</v>
       </c>
       <c r="B231" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>23.43654996790572</v>
+        <v>31.98783579441977</v>
       </c>
     </row>
     <row r="232">
@@ -4135,15 +4135,15 @@
         <v>3</v>
       </c>
       <c r="B232" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>32.86140692304225</v>
+        <v>15.96577866481706</v>
       </c>
     </row>
     <row r="233">
@@ -4151,15 +4151,15 @@
         <v>3</v>
       </c>
       <c r="B233" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>28.10381373259984</v>
+        <v>30.54121131398233</v>
       </c>
     </row>
     <row r="234">
@@ -4167,15 +4167,15 @@
         <v>3</v>
       </c>
       <c r="B234" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>31.064202000713</v>
+        <v>30.45000698383927</v>
       </c>
     </row>
     <row r="235">
@@ -4183,15 +4183,15 @@
         <v>3</v>
       </c>
       <c r="B235" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>31.33778679767613</v>
+        <v>24.98991384848164</v>
       </c>
     </row>
     <row r="236">
@@ -4199,15 +4199,15 @@
         <v>3</v>
       </c>
       <c r="B236" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>23.79061203035931</v>
+        <v>28.89256564630306</v>
       </c>
     </row>
     <row r="237">
@@ -4215,15 +4215,15 @@
         <v>3</v>
       </c>
       <c r="B237" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>32.94001329820139</v>
+        <v>32.09046227818327</v>
       </c>
     </row>
     <row r="238">
@@ -4231,15 +4231,15 @@
         <v>3</v>
       </c>
       <c r="B238" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>27.98794348107915</v>
+        <v>15.79495832299273</v>
       </c>
     </row>
     <row r="239">
@@ -4247,7 +4247,7 @@
         <v>3</v>
       </c>
       <c r="B239" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>30.71429926112531</v>
+        <v>30.09613802764359</v>
       </c>
     </row>
     <row r="240">
@@ -4263,7 +4263,7 @@
         <v>3</v>
       </c>
       <c r="B240" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>31.18567488782448</v>
+        <v>30.55622356415909</v>
       </c>
     </row>
     <row r="241">
@@ -4279,7 +4279,7 @@
         <v>3</v>
       </c>
       <c r="B241" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>23.45347011926101</v>
+        <v>24.79735129227493</v>
       </c>
     </row>
     <row r="242">
@@ -4295,7 +4295,7 @@
         <v>3</v>
       </c>
       <c r="B242" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>30.0771926493718</v>
+        <v>29.02451536523277</v>
       </c>
     </row>
     <row r="243">
@@ -4311,7 +4311,7 @@
         <v>3</v>
       </c>
       <c r="B243" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>32.49877680472856</v>
+        <v>22.36270474569161</v>
       </c>
     </row>
     <row r="244">
@@ -4327,15 +4327,15 @@
         <v>3</v>
       </c>
       <c r="B244" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>27.67140608016031</v>
+        <v>25.24710414769315</v>
       </c>
     </row>
     <row r="245">
@@ -4343,15 +4343,15 @@
         <v>3</v>
       </c>
       <c r="B245" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>35.41986236443987</v>
+        <v>28.83643555795685</v>
       </c>
     </row>
     <row r="246">
@@ -4359,15 +4359,15 @@
         <v>3</v>
       </c>
       <c r="B246" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>15.62421443014278</v>
+        <v>34.15056137677244</v>
       </c>
     </row>
     <row r="247">
@@ -4375,15 +4375,15 @@
         <v>3</v>
       </c>
       <c r="B247" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>29.68320728782728</v>
+        <v>24.03717928657334</v>
       </c>
     </row>
     <row r="248">
@@ -4391,15 +4391,15 @@
         <v>3</v>
       </c>
       <c r="B248" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>32.68064750308575</v>
+        <v>29.3377984289354</v>
       </c>
     </row>
     <row r="249">
@@ -4407,15 +4407,15 @@
         <v>3</v>
       </c>
       <c r="B249" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>28.12055850491996</v>
+        <v>22.32107531592501</v>
       </c>
     </row>
     <row r="250">
@@ -4423,15 +4423,15 @@
         <v>3</v>
       </c>
       <c r="B250" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>34.91046266592422</v>
+        <v>25.02484515905266</v>
       </c>
     </row>
     <row r="251">
@@ -4439,15 +4439,15 @@
         <v>3</v>
       </c>
       <c r="B251" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>15.88216582866741</v>
+        <v>29.0672094852888</v>
       </c>
     </row>
     <row r="252">
@@ -4455,15 +4455,15 @@
         <v>3</v>
       </c>
       <c r="B252" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>30.04436733988203</v>
+        <v>33.93505337503788</v>
       </c>
     </row>
     <row r="253">
@@ -4471,15 +4471,15 @@
         <v>3</v>
       </c>
       <c r="B253" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>32.01663088117122</v>
+        <v>23.64125398313965</v>
       </c>
     </row>
     <row r="254">
@@ -4487,15 +4487,15 @@
         <v>3</v>
       </c>
       <c r="B254" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>27.92083632502852</v>
+        <v>29.0558456028002</v>
       </c>
     </row>
     <row r="255">
@@ -4503,15 +4503,15 @@
         <v>3</v>
       </c>
       <c r="B255" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>34.45899695071206</v>
+        <v>22.38692058250046</v>
       </c>
     </row>
     <row r="256">
@@ -4519,15 +4519,15 @@
         <v>3</v>
       </c>
       <c r="B256" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>15.93689718398524</v>
+        <v>25.22145199606594</v>
       </c>
     </row>
     <row r="257">
@@ -4535,15 +4535,15 @@
         <v>3</v>
       </c>
       <c r="B257" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>30.00385938448724</v>
+        <v>29.42776725204962</v>
       </c>
     </row>
     <row r="258">
@@ -4551,15 +4551,15 @@
         <v>3</v>
       </c>
       <c r="B258" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>32.03981311452571</v>
+        <v>34.72900592267152</v>
       </c>
     </row>
     <row r="259">
@@ -4567,15 +4567,15 @@
         <v>3</v>
       </c>
       <c r="B259" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>27.81002144631781</v>
+        <v>23.94039489463883</v>
       </c>
     </row>
     <row r="260">
@@ -4583,15 +4583,15 @@
         <v>3</v>
       </c>
       <c r="B260" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>34.83719312113126</v>
+        <v>29.26054094834307</v>
       </c>
     </row>
     <row r="261">
@@ -4599,15 +4599,15 @@
         <v>3</v>
       </c>
       <c r="B261" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>15.69402148117423</v>
+        <v>22.20989151065052</v>
       </c>
     </row>
     <row r="262">
@@ -4615,15 +4615,15 @@
         <v>3</v>
       </c>
       <c r="B262" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>29.80098608296634</v>
+        <v>25.13862482788148</v>
       </c>
     </row>
     <row r="263">
@@ -4631,15 +4631,15 @@
         <v>3</v>
       </c>
       <c r="B263" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>32.38522920089999</v>
+        <v>28.91620443972791</v>
       </c>
     </row>
     <row r="264">
@@ -4647,15 +4647,15 @@
         <v>3</v>
       </c>
       <c r="B264" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>27.96803199730778</v>
+        <v>34.54480601747952</v>
       </c>
     </row>
     <row r="265">
@@ -4663,15 +4663,15 @@
         <v>3</v>
       </c>
       <c r="B265" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>34.5180524521346</v>
+        <v>23.78038654071459</v>
       </c>
     </row>
     <row r="266">
@@ -4679,15 +4679,15 @@
         <v>3</v>
       </c>
       <c r="B266" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>15.70865014609354</v>
+        <v>29.41809875462659</v>
       </c>
     </row>
     <row r="267">
@@ -4695,15 +4695,15 @@
         <v>3</v>
       </c>
       <c r="B267" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>30.11777373080908</v>
+        <v>22.7786740566631</v>
       </c>
     </row>
     <row r="268">
@@ -4711,15 +4711,15 @@
         <v>3</v>
       </c>
       <c r="B268" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>31.83867698376608</v>
+        <v>25.11593376917311</v>
       </c>
     </row>
     <row r="269">
@@ -4727,7 +4727,7 @@
         <v>3</v>
       </c>
       <c r="B269" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>27.50700910152905</v>
+        <v>29.11641125899098</v>
       </c>
     </row>
     <row r="270">
@@ -4743,7 +4743,7 @@
         <v>3</v>
       </c>
       <c r="B270" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>34.44467442528113</v>
+        <v>34.6713241225988</v>
       </c>
     </row>
     <row r="271">
@@ -4759,7 +4759,7 @@
         <v>3</v>
       </c>
       <c r="B271" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>15.7493057427014</v>
+        <v>23.88253851028252</v>
       </c>
     </row>
     <row r="272">
@@ -4775,7 +4775,7 @@
         <v>3</v>
       </c>
       <c r="B272" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>30.14146890820769</v>
+        <v>29.33168939578223</v>
       </c>
     </row>
     <row r="273">
@@ -4791,7 +4791,7 @@
         <v>3</v>
       </c>
       <c r="B273" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>32.78313837753706</v>
+        <v>22.43763211993449</v>
       </c>
     </row>
     <row r="274">
@@ -4807,15 +4807,15 @@
         <v>3</v>
       </c>
       <c r="B274" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>28.13897144166699</v>
+        <v>25.16783861203077</v>
       </c>
     </row>
     <row r="275">
@@ -4823,15 +4823,15 @@
         <v>3</v>
       </c>
       <c r="B275" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>34.63844200426617</v>
+        <v>28.7757430184253</v>
       </c>
     </row>
     <row r="276">
@@ -4839,15 +4839,15 @@
         <v>3</v>
       </c>
       <c r="B276" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>15.7799927670798</v>
+        <v>34.44212188971942</v>
       </c>
     </row>
     <row r="277">
@@ -4855,15 +4855,15 @@
         <v>3</v>
       </c>
       <c r="B277" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>29.74680675873302</v>
+        <v>24.09815989481555</v>
       </c>
     </row>
     <row r="278">
@@ -4871,15 +4871,15 @@
         <v>3</v>
       </c>
       <c r="B278" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>32.30052143938359</v>
+        <v>29.69079948207868</v>
       </c>
     </row>
     <row r="279">
@@ -4887,15 +4887,15 @@
         <v>3</v>
       </c>
       <c r="B279" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>27.81915223347374</v>
+        <v>22.65001759793227</v>
       </c>
     </row>
     <row r="280">
@@ -4903,15 +4903,15 @@
         <v>3</v>
       </c>
       <c r="B280" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>34.80589472198484</v>
+        <v>25.68466032383</v>
       </c>
     </row>
     <row r="281">
@@ -4919,15 +4919,15 @@
         <v>3</v>
       </c>
       <c r="B281" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>15.65243228308498</v>
+        <v>28.7773850577043</v>
       </c>
     </row>
     <row r="282">
@@ -4935,15 +4935,15 @@
         <v>3</v>
       </c>
       <c r="B282" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>31.5465064656382</v>
+        <v>34.73405424946419</v>
       </c>
     </row>
     <row r="283">
@@ -4951,15 +4951,15 @@
         <v>3</v>
       </c>
       <c r="B283" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>28.67663445871264</v>
+        <v>24.02270926287277</v>
       </c>
     </row>
     <row r="284">
@@ -4967,15 +4967,15 @@
         <v>3</v>
       </c>
       <c r="B284" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>27.13323713947479</v>
+        <v>29.90697630509682</v>
       </c>
     </row>
     <row r="285">
@@ -4983,15 +4983,15 @@
         <v>3</v>
       </c>
       <c r="B285" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>30.39690168762309</v>
+        <v>22.25346687849758</v>
       </c>
     </row>
     <row r="286">
@@ -4999,15 +4999,15 @@
         <v>3</v>
       </c>
       <c r="B286" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>18.37442202986499</v>
+        <v>24.93214602647758</v>
       </c>
     </row>
     <row r="287">
@@ -5015,15 +5015,15 @@
         <v>3</v>
       </c>
       <c r="B287" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>31.25760016663242</v>
+        <v>28.82609184133769</v>
       </c>
     </row>
     <row r="288">
@@ -5031,15 +5031,15 @@
         <v>3</v>
       </c>
       <c r="B288" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>28.30702387059335</v>
+        <v>33.70234663165332</v>
       </c>
     </row>
     <row r="289">
@@ -5047,15 +5047,15 @@
         <v>3</v>
       </c>
       <c r="B289" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>27.16619986474345</v>
+        <v>23.85267668671973</v>
       </c>
     </row>
     <row r="290">
@@ -5063,15 +5063,15 @@
         <v>3</v>
       </c>
       <c r="B290" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>30.30485404421071</v>
+        <v>26.45301894287697</v>
       </c>
     </row>
     <row r="291">
@@ -5079,15 +5079,15 @@
         <v>3</v>
       </c>
       <c r="B291" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>18.10741868771996</v>
+        <v>26.63507762620971</v>
       </c>
     </row>
     <row r="292">
@@ -5095,15 +5095,15 @@
         <v>3</v>
       </c>
       <c r="B292" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>31.39120941745782</v>
+        <v>29.67112573435474</v>
       </c>
     </row>
     <row r="293">
@@ -5111,15 +5111,15 @@
         <v>3</v>
       </c>
       <c r="B293" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>28.38438509277034</v>
+        <v>29.46310115289606</v>
       </c>
     </row>
     <row r="294">
@@ -5127,15 +5127,15 @@
         <v>3</v>
       </c>
       <c r="B294" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>27.55695035592944</v>
+        <v>28.68074163836922</v>
       </c>
     </row>
     <row r="295">
@@ -5143,15 +5143,15 @@
         <v>3</v>
       </c>
       <c r="B295" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>30.56570428050935</v>
+        <v>27.84019991018853</v>
       </c>
     </row>
     <row r="296">
@@ -5159,15 +5159,15 @@
         <v>3</v>
       </c>
       <c r="B296" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>18.64140432972898</v>
+        <v>26.41589280984012</v>
       </c>
     </row>
     <row r="297">
@@ -5175,15 +5175,15 @@
         <v>3</v>
       </c>
       <c r="B297" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>31.14269660782436</v>
+        <v>26.72590657652815</v>
       </c>
     </row>
     <row r="298">
@@ -5191,15 +5191,15 @@
         <v>3</v>
       </c>
       <c r="B298" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>28.49010769206039</v>
+        <v>29.1796743985436</v>
       </c>
     </row>
     <row r="299">
@@ -5207,7 +5207,7 @@
         <v>3</v>
       </c>
       <c r="B299" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>27.21258020329609</v>
+        <v>29.45017019633031</v>
       </c>
     </row>
     <row r="300">
@@ -5223,7 +5223,7 @@
         <v>3</v>
       </c>
       <c r="B300" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>30.93825135010016</v>
+        <v>28.74580681175474</v>
       </c>
     </row>
     <row r="301">
@@ -5239,7 +5239,7 @@
         <v>3</v>
       </c>
       <c r="B301" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>18.10097907214637</v>
+        <v>27.8703656288721</v>
       </c>
     </row>
     <row r="302">
@@ -5255,7 +5255,7 @@
         <v>3</v>
       </c>
       <c r="B302" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>31.11998301338879</v>
+        <v>26.1987262290957</v>
       </c>
     </row>
     <row r="303">
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="B303" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>28.07444093991229</v>
+        <v>26.95514372273376</v>
       </c>
     </row>
     <row r="304">
@@ -5287,15 +5287,15 @@
         <v>3</v>
       </c>
       <c r="B304" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>26.58587030801819</v>
+        <v>29.5361987486131</v>
       </c>
     </row>
     <row r="305">
@@ -5303,15 +5303,15 @@
         <v>3</v>
       </c>
       <c r="B305" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>30.11610851243058</v>
+        <v>29.27848581201093</v>
       </c>
     </row>
     <row r="306">
@@ -5319,15 +5319,15 @@
         <v>3</v>
       </c>
       <c r="B306" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>18.10995105177889</v>
+        <v>27.95773102070302</v>
       </c>
     </row>
     <row r="307">
@@ -5335,15 +5335,15 @@
         <v>3</v>
       </c>
       <c r="B307" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>31.43071612262892</v>
+        <v>27.83390753567346</v>
       </c>
     </row>
     <row r="308">
@@ -5351,15 +5351,15 @@
         <v>3</v>
       </c>
       <c r="B308" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>28.34025643224533</v>
+        <v>26.65676627909538</v>
       </c>
     </row>
     <row r="309">
@@ -5367,15 +5367,15 @@
         <v>3</v>
       </c>
       <c r="B309" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>27.67239956526968</v>
+        <v>26.60757480459009</v>
       </c>
     </row>
     <row r="310">
@@ -5383,15 +5383,15 @@
         <v>3</v>
       </c>
       <c r="B310" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>30.56302582994522</v>
+        <v>29.43698359191132</v>
       </c>
     </row>
     <row r="311">
@@ -5399,15 +5399,15 @@
         <v>3</v>
       </c>
       <c r="B311" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>18.14320507772015</v>
+        <v>29.10063444108391</v>
       </c>
     </row>
     <row r="312">
@@ -5415,15 +5415,15 @@
         <v>3</v>
       </c>
       <c r="B312" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>31.10156313921502</v>
+        <v>28.10740074437057</v>
       </c>
     </row>
     <row r="313">
@@ -5431,15 +5431,15 @@
         <v>3</v>
       </c>
       <c r="B313" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>28.38266812249601</v>
+        <v>27.96187425167716</v>
       </c>
     </row>
     <row r="314">
@@ -5447,15 +5447,15 @@
         <v>3</v>
       </c>
       <c r="B314" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>26.80416738486019</v>
+        <v>26.68743379559405</v>
       </c>
     </row>
     <row r="315">
@@ -5463,15 +5463,15 @@
         <v>3</v>
       </c>
       <c r="B315" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>30.82976164171924</v>
+        <v>26.73189569886224</v>
       </c>
     </row>
     <row r="316">
@@ -5479,15 +5479,15 @@
         <v>3</v>
       </c>
       <c r="B316" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>18.46371114214148</v>
+        <v>29.78049326423044</v>
       </c>
     </row>
     <row r="317">
@@ -5495,15 +5495,15 @@
         <v>3</v>
       </c>
       <c r="B317" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>31.23627344091754</v>
+        <v>28.59525095593398</v>
       </c>
     </row>
     <row r="318">
@@ -5511,15 +5511,15 @@
         <v>3</v>
       </c>
       <c r="B318" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>27.75987866945029</v>
+        <v>27.97486651654892</v>
       </c>
     </row>
     <row r="319">
@@ -5527,15 +5527,15 @@
         <v>3</v>
       </c>
       <c r="B319" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>27.53052878530078</v>
+        <v>28.35951476904194</v>
       </c>
     </row>
     <row r="320">
@@ -5543,15 +5543,15 @@
         <v>3</v>
       </c>
       <c r="B320" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>30.24060506807639</v>
+        <v>26.74394807625156</v>
       </c>
     </row>
     <row r="321">
@@ -5559,15 +5559,1039 @@
         <v>3</v>
       </c>
       <c r="B321" t="n">
+        <v>54</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>26.39601968269633</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>3</v>
+      </c>
+      <c r="B322" t="n">
+        <v>54</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>30.02874495700152</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>3</v>
+      </c>
+      <c r="B323" t="n">
+        <v>54</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>28.95395679325184</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>3</v>
+      </c>
+      <c r="B324" t="n">
+        <v>54</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>28.74576620242208</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>3</v>
+      </c>
+      <c r="B325" t="n">
+        <v>54</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>28.02064934077672</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>3</v>
+      </c>
+      <c r="B326" t="n">
+        <v>55</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>27.2046685059067</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>3</v>
+      </c>
+      <c r="B327" t="n">
+        <v>55</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>27.06191458416295</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>3</v>
+      </c>
+      <c r="B328" t="n">
+        <v>55</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>29.4964493903923</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>3</v>
+      </c>
+      <c r="B329" t="n">
+        <v>55</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>29.20148631410503</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>3</v>
+      </c>
+      <c r="B330" t="n">
+        <v>55</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>28.59407533873767</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>3</v>
+      </c>
+      <c r="B331" t="n">
+        <v>55</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>28.38498368035059</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>3</v>
+      </c>
+      <c r="B332" t="n">
+        <v>56</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>26.39816464695118</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>3</v>
+      </c>
+      <c r="B333" t="n">
+        <v>56</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>26.77753621449802</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>3</v>
+      </c>
+      <c r="B334" t="n">
+        <v>56</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>29.88304510226989</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>3</v>
+      </c>
+      <c r="B335" t="n">
+        <v>56</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>28.41186679923126</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>3</v>
+      </c>
+      <c r="B336" t="n">
+        <v>56</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>28.07454713302252</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>3</v>
+      </c>
+      <c r="B337" t="n">
+        <v>56</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>27.43072243577382</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>3</v>
+      </c>
+      <c r="B338" t="n">
+        <v>57</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>29.2026384638177</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>3</v>
+      </c>
+      <c r="B339" t="n">
+        <v>57</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>30.93257902903899</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>3</v>
+      </c>
+      <c r="B340" t="n">
+        <v>57</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>23.61147112517853</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>3</v>
+      </c>
+      <c r="B341" t="n">
+        <v>57</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>27.10261274250927</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>3</v>
+      </c>
+      <c r="B342" t="n">
+        <v>57</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>29.29310240126282</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>3</v>
+      </c>
+      <c r="B343" t="n">
+        <v>57</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>20.01223748859628</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>3</v>
+      </c>
+      <c r="B344" t="n">
+        <v>58</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>28.78274854010469</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>3</v>
+      </c>
+      <c r="B345" t="n">
+        <v>58</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>30.69514604979343</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>3</v>
+      </c>
+      <c r="B346" t="n">
+        <v>58</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>23.35133421147205</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>3</v>
+      </c>
+      <c r="B347" t="n">
+        <v>58</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>27.0736914193375</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>3</v>
+      </c>
+      <c r="B348" t="n">
+        <v>58</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>28.22776273769819</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>3</v>
+      </c>
+      <c r="B349" t="n">
+        <v>58</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>20.27420720390161</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>3</v>
+      </c>
+      <c r="B350" t="n">
+        <v>59</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>28.89955633159597</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>3</v>
+      </c>
+      <c r="B351" t="n">
+        <v>59</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>30.9178771860367</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>3</v>
+      </c>
+      <c r="B352" t="n">
+        <v>59</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>23.34727099198109</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>3</v>
+      </c>
+      <c r="B353" t="n">
+        <v>59</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>26.82800261414788</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>3</v>
+      </c>
+      <c r="B354" t="n">
+        <v>59</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>28.67556020763989</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>3</v>
+      </c>
+      <c r="B355" t="n">
+        <v>59</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>20.07735300467299</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>3</v>
+      </c>
+      <c r="B356" t="n">
+        <v>60</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>29.2631714976385</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>3</v>
+      </c>
+      <c r="B357" t="n">
+        <v>60</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>31.00555125030442</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>3</v>
+      </c>
+      <c r="B358" t="n">
+        <v>60</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>23.03269341063235</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>3</v>
+      </c>
+      <c r="B359" t="n">
+        <v>60</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>27.21905461889997</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>3</v>
+      </c>
+      <c r="B360" t="n">
+        <v>60</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>28.67083580515452</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>3</v>
+      </c>
+      <c r="B361" t="n">
+        <v>60</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>20.13139963433389</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>3</v>
+      </c>
+      <c r="B362" t="n">
+        <v>61</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
+        <v>29.25018477161604</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>3</v>
+      </c>
+      <c r="B363" t="n">
+        <v>61</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>30.39426021910589</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>3</v>
+      </c>
+      <c r="B364" t="n">
+        <v>61</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D364" t="n">
+        <v>23.13320307159</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>3</v>
+      </c>
+      <c r="B365" t="n">
+        <v>61</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D365" t="n">
+        <v>26.75813015836751</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>3</v>
+      </c>
+      <c r="B366" t="n">
+        <v>61</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D366" t="n">
+        <v>29.38998153818003</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>3</v>
+      </c>
+      <c r="B367" t="n">
+        <v>61</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D367" t="n">
+        <v>20.29944748511542</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>3</v>
+      </c>
+      <c r="B368" t="n">
+        <v>62</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D368" t="n">
+        <v>29.07663459430304</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>3</v>
+      </c>
+      <c r="B369" t="n">
+        <v>62</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D369" t="n">
+        <v>30.77792392441868</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>3</v>
+      </c>
+      <c r="B370" t="n">
+        <v>62</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D370" t="n">
+        <v>23.23586319089648</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>3</v>
+      </c>
+      <c r="B371" t="n">
+        <v>62</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D371" t="n">
+        <v>27.02270179610979</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>3</v>
+      </c>
+      <c r="B372" t="n">
+        <v>62</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D372" t="n">
+        <v>29.00070095750247</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>3</v>
+      </c>
+      <c r="B373" t="n">
+        <v>62</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D373" t="n">
+        <v>20.44600737647483</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>3</v>
+      </c>
+      <c r="B374" t="n">
+        <v>63</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D374" t="n">
+        <v>29.12618606751351</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>3</v>
+      </c>
+      <c r="B375" t="n">
+        <v>63</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D375" t="n">
+        <v>30.53535948939236</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>3</v>
+      </c>
+      <c r="B376" t="n">
+        <v>63</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D376" t="n">
+        <v>23.1980104275224</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>3</v>
+      </c>
+      <c r="B377" t="n">
+        <v>63</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D377" t="n">
+        <v>26.4591271314441</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>3</v>
+      </c>
+      <c r="B378" t="n">
+        <v>63</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D378" t="n">
+        <v>28.38694178501519</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>3</v>
+      </c>
+      <c r="B379" t="n">
+        <v>63</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D379" t="n">
+        <v>20.56966181583805</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>3</v>
+      </c>
+      <c r="B380" t="n">
         <v>64</v>
       </c>
-      <c r="C321" t="inlineStr">
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D380" t="n">
+        <v>29.76319652362181</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>3</v>
+      </c>
+      <c r="B381" t="n">
+        <v>64</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D381" t="n">
+        <v>30.63572151207531</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>3</v>
+      </c>
+      <c r="B382" t="n">
+        <v>64</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D382" t="n">
+        <v>23.39611157388414</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>3</v>
+      </c>
+      <c r="B383" t="n">
+        <v>64</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D383" t="n">
+        <v>27.16684045577297</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>3</v>
+      </c>
+      <c r="B384" t="n">
+        <v>64</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>29.71112215511457</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>3</v>
+      </c>
+      <c r="B385" t="n">
+        <v>64</v>
+      </c>
+      <c r="C385" t="inlineStr">
         <is>
           <t>EASINGTON</t>
         </is>
       </c>
-      <c r="D321" t="n">
-        <v>18.47436391044671</v>
+      <c r="D385" t="n">
+        <v>20.51947910913864</v>
       </c>
     </row>
   </sheetData>
